--- a/役員提案_根拠データ.xlsx
+++ b/役員提案_根拠データ.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="460">
   <si>
     <t xml:space="preserve">前提条件（黄色セルを変更すると全シートが再計算されます）</t>
   </si>
@@ -399,6 +399,90 @@
   </si>
   <si>
     <t xml:space="preserve">仮定。在庫取崩しなし（横ばい）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下期の値上げ適用月数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">か月</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月中旬開始の場合：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3/31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">予算原価率</t>
@@ -4421,6 +4505,27 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月中旬開始・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">A</t>
     </r>
     <r>
@@ -4452,11 +4557,48 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案、弾力性反映）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">品目別試算（出数ベース）</t>
+      <t xml:space="preserve">案）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">品目別試算（出数ベース）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">適用月数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/6</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">＋原価コントロール（必要額）</t>
@@ -4518,7 +4660,28 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">一律）</t>
+      <t xml:space="preserve">一律・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月中旬開始）</t>
     </r>
   </si>
   <si>
@@ -6119,7 +6282,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -6376,58 +6539,72 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B21" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="11" t="n">
         <f aca="false">B8/B7</f>
         <v>0.333983870811215</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="11" t="n">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="11" t="n">
         <f aca="false">B6/B5</f>
         <v>0.364222912297552</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <f aca="false">B12/(B17/1000)</f>
-        <v>2.07100436931419</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="12" t="n">
+        <f aca="false">B12/(B17/1000)</f>
+        <v>2.07100436931419</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="13" t="n">
         <f aca="false">B15-B16</f>
         <v>465.208</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>38</v>
+      <c r="D26" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -6462,73 +6639,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>843</v>
@@ -6574,18 +6751,18 @@
         <v>48688.0514347826</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>338</v>
@@ -6634,13 +6811,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>336</v>
@@ -6689,13 +6866,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>217</v>
@@ -6744,13 +6921,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>184</v>
@@ -6799,13 +6976,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>89</v>
@@ -6854,13 +7031,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>86</v>
@@ -6909,13 +7086,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>78</v>
@@ -6964,13 +7141,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>70</v>
@@ -7019,13 +7196,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>79</v>
@@ -7074,13 +7251,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>249</v>
@@ -7129,13 +7306,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>40</v>
@@ -7184,13 +7361,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>354</v>
@@ -7236,18 +7413,18 @@
         <v>13593.6</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>43</v>
@@ -7296,13 +7473,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>23</v>
@@ -7351,13 +7528,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>28</v>
@@ -7406,13 +7583,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>14</v>
@@ -7461,13 +7638,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>24</v>
@@ -7516,13 +7693,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>13</v>
@@ -7571,13 +7748,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>19</v>
@@ -7626,13 +7803,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>17</v>
@@ -7681,13 +7858,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>10</v>
@@ -7736,13 +7913,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>9</v>
@@ -7791,13 +7968,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>21</v>
@@ -7846,13 +8023,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>4</v>
@@ -7901,13 +8078,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>9</v>
@@ -7956,13 +8133,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>10</v>
@@ -8011,13 +8188,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>3</v>
@@ -8063,18 +8240,18 @@
         <v>115.2</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>416</v>
@@ -8123,13 +8300,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>279</v>
@@ -8178,13 +8355,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>327</v>
@@ -8233,13 +8410,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>281</v>
@@ -8288,13 +8465,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>180</v>
@@ -8343,13 +8520,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>80</v>
@@ -8398,13 +8575,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>128</v>
@@ -8453,13 +8630,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>97</v>
@@ -8508,13 +8685,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>44</v>
@@ -8563,13 +8740,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>65</v>
@@ -8618,13 +8795,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>39</v>
@@ -8673,13 +8850,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>72</v>
@@ -8728,13 +8905,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>54</v>
@@ -8783,13 +8960,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>48</v>
@@ -8838,13 +9015,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>26</v>
@@ -8893,13 +9070,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>58</v>
@@ -8948,13 +9125,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>34</v>
@@ -9003,13 +9180,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>36</v>
@@ -9058,13 +9235,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>35</v>
@@ -9113,13 +9290,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>30</v>
@@ -9168,13 +9345,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>26</v>
@@ -9223,13 +9400,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>58</v>
@@ -9278,13 +9455,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>25</v>
@@ -9333,13 +9510,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>21</v>
@@ -9388,13 +9565,13 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>17</v>
@@ -9443,13 +9620,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>6</v>
@@ -9498,13 +9675,13 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>18</v>
@@ -9553,13 +9730,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>15</v>
@@ -9608,13 +9785,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>23</v>
@@ -9663,13 +9840,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>7</v>
@@ -9718,13 +9895,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>13</v>
@@ -9773,13 +9950,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>17</v>
@@ -9828,13 +10005,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>4</v>
@@ -9883,13 +10060,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>11</v>
@@ -9938,13 +10115,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>12</v>
@@ -9993,13 +10170,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>10</v>
@@ -10048,13 +10225,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>7</v>
@@ -10103,13 +10280,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3</v>
@@ -10158,13 +10335,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>4</v>
@@ -10213,13 +10390,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2134</v>
@@ -10265,18 +10442,18 @@
         <v>28925.7963385389</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>165</v>
@@ -10325,13 +10502,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>107</v>
@@ -10380,13 +10557,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>193</v>
@@ -10435,13 +10612,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>136</v>
@@ -10490,13 +10667,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>74</v>
@@ -10545,13 +10722,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>114</v>
@@ -10600,13 +10777,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>112</v>
@@ -10655,13 +10832,13 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>109</v>
@@ -10710,13 +10887,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>50</v>
@@ -10765,13 +10942,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>84</v>
@@ -10820,13 +10997,13 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>81</v>
@@ -10875,13 +11052,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>75</v>
@@ -10930,13 +11107,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>71</v>
@@ -10985,13 +11162,13 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>69</v>
@@ -11040,13 +11217,13 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>35</v>
@@ -11095,13 +11272,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>56</v>
@@ -11150,13 +11327,13 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>30</v>
@@ -11205,13 +11382,13 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>26</v>
@@ -11260,13 +11437,13 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>25</v>
@@ -11315,13 +11492,13 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>37</v>
@@ -11370,13 +11547,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>9</v>
@@ -11425,13 +11602,13 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>443</v>
@@ -11480,13 +11657,13 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>181</v>
@@ -11535,13 +11712,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>161</v>
@@ -11590,13 +11767,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>85</v>
@@ -11645,13 +11822,13 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>80</v>
@@ -11700,13 +11877,13 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>74</v>
@@ -11755,13 +11932,13 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>45</v>
@@ -11810,13 +11987,13 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D101" s="7" t="n">
         <v>40</v>
@@ -11865,13 +12042,13 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>31</v>
@@ -11920,13 +12097,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D103" s="7" t="n">
         <v>24</v>
@@ -11975,13 +12152,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>22</v>
@@ -12030,13 +12207,13 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D105" s="7" t="n">
         <v>20</v>
@@ -12085,13 +12262,13 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>299</v>
@@ -12140,13 +12317,13 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D107" s="7" t="n">
         <v>117</v>
@@ -12195,13 +12372,13 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>280</v>
@@ -12250,13 +12427,13 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D109" s="7" t="n">
         <v>145</v>
@@ -12305,13 +12482,13 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>200</v>
@@ -12360,13 +12537,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>50</v>
@@ -12415,13 +12592,13 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>118</v>
@@ -12470,13 +12647,13 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>163</v>
@@ -12525,13 +12702,13 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>96</v>
@@ -12580,13 +12757,13 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>103</v>
@@ -12635,13 +12812,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>34</v>
@@ -12690,13 +12867,13 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>112</v>
@@ -12745,13 +12922,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>142</v>
@@ -12800,13 +12977,13 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>103</v>
@@ -12855,13 +13032,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>73</v>
@@ -12910,13 +13087,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>106</v>
@@ -12965,13 +13142,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>92</v>
@@ -13020,13 +13197,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>76</v>
@@ -13075,13 +13252,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>45</v>
@@ -13130,13 +13307,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>103</v>
@@ -13185,13 +13362,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>58</v>
@@ -13240,13 +13417,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D127" s="7" t="n">
         <v>44</v>
@@ -13295,13 +13472,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>67</v>
@@ -13350,13 +13527,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D129" s="7" t="n">
         <v>46</v>
@@ -13405,13 +13582,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>46</v>
@@ -13460,13 +13637,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>34</v>
@@ -13515,13 +13692,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>55</v>
@@ -13570,13 +13747,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>34</v>
@@ -13625,13 +13802,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>39</v>
@@ -13680,13 +13857,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>24</v>
@@ -13735,13 +13912,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>22</v>
@@ -13790,13 +13967,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>16</v>
@@ -13845,13 +14022,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>21</v>
@@ -13900,13 +14077,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D139" s="7" t="n">
         <v>21</v>
@@ -13955,13 +14132,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>11</v>
@@ -14010,13 +14187,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>8</v>
@@ -14065,13 +14242,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>4</v>
@@ -14120,13 +14297,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>6</v>
@@ -14175,13 +14352,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>677</v>
@@ -14230,13 +14407,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D145" s="7" t="n">
         <v>204</v>
@@ -14285,13 +14462,13 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>178</v>
@@ -14340,13 +14517,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D147" s="7" t="n">
         <v>101</v>
@@ -14395,13 +14572,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>128</v>
@@ -14450,13 +14627,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D149" s="7" t="n">
         <v>84</v>
@@ -14505,13 +14682,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>78</v>
@@ -14560,13 +14737,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>121</v>
@@ -14615,13 +14792,13 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>51</v>
@@ -14670,13 +14847,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D153" s="7" t="n">
         <v>24</v>
@@ -14725,13 +14902,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>2</v>
@@ -14780,13 +14957,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>964</v>
@@ -14832,12 +15009,12 @@
         <v>33919.498051948</v>
       </c>
       <c r="P155" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B156" s="19"/>
       <c r="C156" s="19"/>
@@ -14878,7 +15055,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="22" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -14912,49 +15089,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">SUMIF(品目別試算!$C$5:$C$155,$A5,品目別試算!$K$5:$K$155)</f>
@@ -14985,17 +15162,17 @@
         <v>0.319786983157315</v>
       </c>
       <c r="I5" s="18" t="n">
-        <f aca="false">C5/1000*前提!$B$24*2</f>
+        <f aca="false">C5/1000*前提!$B$25*2</f>
         <v>538.329933423475</v>
       </c>
       <c r="J5" s="18" t="n">
-        <f aca="false">F5/1000*前提!$B$24*2</f>
+        <f aca="false">F5/1000*前提!$B$25*2</f>
         <v>622.433919425033</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">SUMIF(品目別試算!$C$5:$C$155,$A6,品目別試算!$K$5:$K$155)</f>
@@ -15026,17 +15203,17 @@
         <v>0.284933697149386</v>
       </c>
       <c r="I6" s="18" t="n">
-        <f aca="false">C6/1000*前提!$B$24*2</f>
+        <f aca="false">C6/1000*前提!$B$25*2</f>
         <v>205.313142996802</v>
       </c>
       <c r="J6" s="18" t="n">
-        <f aca="false">F6/1000*前提!$B$24*2</f>
+        <f aca="false">F6/1000*前提!$B$25*2</f>
         <v>232.545573760701</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">SUMIF(品目別試算!$C$5:$C$155,$A7,品目別試算!$K$5:$K$155)</f>
@@ -15067,17 +15244,17 @@
         <v>0.322159189926267</v>
       </c>
       <c r="I7" s="18" t="n">
-        <f aca="false">C7/1000*前提!$B$24*2</f>
+        <f aca="false">C7/1000*前提!$B$25*2</f>
         <v>273.695539742722</v>
       </c>
       <c r="J7" s="18" t="n">
-        <f aca="false">F7/1000*前提!$B$24*2</f>
+        <f aca="false">F7/1000*前提!$B$25*2</f>
         <v>313.531174833885</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">SUMIF(品目別試算!$C$5:$C$155,$A8,品目別試算!$K$5:$K$155)</f>
@@ -15108,17 +15285,17 @@
         <v>0.319432474490322</v>
       </c>
       <c r="I8" s="18" t="n">
-        <f aca="false">C8/1000*前提!$B$24*2</f>
+        <f aca="false">C8/1000*前提!$B$25*2</f>
         <v>129.525518122301</v>
       </c>
       <c r="J8" s="18" t="n">
-        <f aca="false">F8/1000*前提!$B$24*2</f>
+        <f aca="false">F8/1000*前提!$B$25*2</f>
         <v>152.982380651855</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">SUMIF(品目別試算!$C$5:$C$155,$A9,品目別試算!$K$5:$K$155)</f>
@@ -15149,17 +15326,17 @@
         <v>0.2066727442159</v>
       </c>
       <c r="I9" s="18" t="n">
-        <f aca="false">C9/1000*前提!$B$24*2</f>
+        <f aca="false">C9/1000*前提!$B$25*2</f>
         <v>228.395365000622</v>
       </c>
       <c r="J9" s="18" t="n">
-        <f aca="false">F9/1000*前提!$B$24*2</f>
+        <f aca="false">F9/1000*前提!$B$25*2</f>
         <v>249.728347672252</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUMIF(品目別試算!$C$5:$C$155,$A10,品目別試算!$K$5:$K$155)</f>
@@ -15190,17 +15367,17 @@
         <v>0.224491368256011</v>
       </c>
       <c r="I10" s="18" t="n">
-        <f aca="false">C10/1000*前提!$B$24*2</f>
+        <f aca="false">C10/1000*前提!$B$25*2</f>
         <v>88.4787551240517</v>
       </c>
       <c r="J10" s="18" t="n">
-        <f aca="false">F10/1000*前提!$B$24*2</f>
+        <f aca="false">F10/1000*前提!$B$25*2</f>
         <v>97.4944740047819</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="false">SUM(B5:B10)</f>
@@ -15241,7 +15418,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D13" s="27" t="n">
         <f aca="false">SUMPRODUCT(品目別試算!$D$5:$D$155,品目別試算!$G$5:$G$155-品目別試算!$E$5:$E$155)/前提!B17</f>
@@ -15250,7 +15427,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -15280,37 +15457,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B5" s="13" t="n">
         <f aca="false">前提!B5</f>
@@ -15331,14 +15508,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">前提!B5*前提!B19</f>
         <v>54943.438</v>
       </c>
       <c r="C6" s="13" t="n">
-        <f aca="false">(前提!B6-前提!$B$25)*前提!B19-前提!B20</f>
+        <f aca="false">(前提!B6-前提!$B$26)*前提!B19-前提!B20</f>
         <v>19546.451</v>
       </c>
       <c r="D6" s="28" t="n">
@@ -15350,44 +15527,44 @@
         <v>-0.846703477128602</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B7" s="13" t="n">
-        <f aca="false">B6+効果サマリー!C11/1000*前提!$B$24</f>
-        <v>55675.307127205</v>
+        <f aca="false">B6+効果サマリー!C11/1000*前提!$B$25*前提!B21/6</f>
+        <v>55370.3616575363</v>
       </c>
       <c r="C7" s="13" t="n">
-        <f aca="false">C6+効果サマリー!E11/1000*前提!$B$24</f>
-        <v>19443.9621920307</v>
+        <f aca="false">C6+効果サマリー!E11/1000*前提!$B$25*前提!B21/6</f>
+        <v>19486.6658620179</v>
       </c>
       <c r="D7" s="28" t="n">
         <f aca="false">C7/B7</f>
-        <v>0.349238525934053</v>
+        <v>0.351933151214404</v>
       </c>
       <c r="E7" s="29" t="n">
         <f aca="false">(D7-D6)*100</f>
-        <v>-0.651735159221339</v>
+        <v>-0.382272631186242</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B8" s="13" t="n">
         <f aca="false">B7</f>
-        <v>55675.307127205</v>
+        <v>55370.3616575363</v>
       </c>
       <c r="C8" s="13" t="n">
-        <f aca="false">B7*前提!$B$22</f>
-        <v>18594.6545829471</v>
+        <f aca="false">B7*前提!$B$23</f>
+        <v>18492.8077146008</v>
       </c>
       <c r="D8" s="28" t="n">
         <f aca="false">C8/B8</f>
@@ -15395,78 +15572,78 @@
       </c>
       <c r="E8" s="29" t="n">
         <f aca="false">(D8-D7)*100</f>
-        <v>-1.52546551228381</v>
+        <v>-1.79492804031891</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B10" s="30" t="n">
         <f aca="false">C7-C8</f>
-        <v>849.3076090836</v>
+        <v>993.858147417108</v>
       </c>
       <c r="C10" s="26" t="n">
         <f aca="false">B10/C7</f>
-        <v>0.043679760364464</v>
+        <v>0.0510019597223283</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="31" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">B5+B8</f>
-        <v>110618.745127205</v>
+        <v>110313.799657536</v>
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">C5+C8</f>
-        <v>38606.3135829471</v>
+        <v>38504.4667146008</v>
       </c>
       <c r="D12" s="28" t="n">
         <f aca="false">C12/B12</f>
-        <v>0.349003358685295</v>
+        <v>0.349044877740918</v>
       </c>
       <c r="E12" s="29" t="n">
-        <f aca="false">(D12-前提!$B$22)*100</f>
-        <v>1.50194878740801</v>
+        <f aca="false">(D12-前提!$B$23)*100</f>
+        <v>1.50610069297029</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">B8</f>
-        <v>55675.307127205</v>
+        <v>55370.3616575363</v>
       </c>
       <c r="C13" s="13" t="n">
-        <f aca="false">前提!$B$22*(B5+B8)-C5</f>
-        <v>16933.2176818631</v>
+        <f aca="false">前提!$B$23*(B5+B8)-C5</f>
+        <v>16831.3708135168</v>
       </c>
       <c r="D13" s="28" t="n">
         <f aca="false">C13/B13</f>
-        <v>0.304142330875242</v>
+        <v>0.303977982257336</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">C8-C13</f>
@@ -15476,19 +15653,19 @@
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D16" s="27" t="n">
-        <f aca="false">(C6/前提!$B$22-B6)/前提!B12</f>
-        <v>0.122634724460421</v>
+        <f aca="false">(C6/前提!$B$23-B6)/(前提!B12*前提!B21/6)</f>
+        <v>0.210230956217864</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -15518,47 +15695,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="32" t="n">
-        <f aca="false">前提!$B$22</f>
+        <f aca="false">前提!$B$23</f>
         <v>0.333983870811215</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B6" s="13" t="n">
-        <f aca="false">前提!B9*前提!B11/前提!B10+前提!B12*前提!B14/前提!B13-前提!$B$22*前提!B5</f>
+        <f aca="false">前提!B9*前提!B11/前提!B10+前提!B12*前提!B14/前提!B13-前提!$B$23*前提!B5</f>
         <v>107.864631084016</v>
       </c>
       <c r="C6" s="29" t="n">
@@ -15566,15 +15743,15 @@
         <v>0.196319405938915</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B7" s="13" t="n">
-        <f aca="false">前提!$B$25</f>
+        <f aca="false">前提!$B$26</f>
         <v>465.208</v>
       </c>
       <c r="C7" s="29" t="n">
@@ -15582,15 +15759,15 @@
         <v>0.846703477128607</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B8" s="13" t="n">
-        <f aca="false">前提!B6-前提!$B$22*前提!B5-B6-B7</f>
+        <f aca="false">前提!B6-前提!$B$23*前提!B5-B6-B7</f>
         <v>1088.36427</v>
       </c>
       <c r="C8" s="29" t="n">
@@ -15598,28 +15775,28 @@
         <v>1.98088126556623</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B9" s="30" t="n">
-        <f aca="false">前提!B6-前提!$B$22*前提!B5</f>
+        <f aca="false">前提!B6-前提!$B$23*前提!B5</f>
         <v>1661.43690108401</v>
       </c>
       <c r="C9" s="33" t="n">
-        <f aca="false">前提!$B$23</f>
+        <f aca="false">前提!$B$24</f>
         <v>0.364222912297552</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -15651,417 +15828,417 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>429</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>390</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>499</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>410</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>780</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1180</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1800</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>1940</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>1650</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>550</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>1100</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>550</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>850</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>600</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>1290</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1200</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>850</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>500</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
